--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_24-10-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_24-10-2025.xlsx
@@ -591,25 +591,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6fcd8e8e5+80021]
-	GetHandleVerifier [0x0x7ff6fcd8e940+80112]
-	(No symbol) [0x0x7ff6fcb1060f]
-	(No symbol) [0x0x7ff6fcb68854]
-	(No symbol) [0x0x7ff6fcb68b1c]
-	(No symbol) [0x0x7ff6fcbbc927]
-	(No symbol) [0x0x7ff6fcb9126f]
-	(No symbol) [0x0x7ff6fcbb968a]
-	(No symbol) [0x0x7ff6fcb91003]
-	(No symbol) [0x0x7ff6fcb595d1]
-	(No symbol) [0x0x7ff6fcb5a3f3]
-	GetHandleVerifier [0x0x7ff6fd04dc7d+2960429]
-	GetHandleVerifier [0x0x7ff6fd047f3a+2936554]
-	GetHandleVerifier [0x0x7ff6fd068977+3070247]
-	GetHandleVerifier [0x0x7ff6fcda83ce+185214]
-	GetHandleVerifier [0x0x7ff6fcdafe1f+216527]
-	GetHandleVerifier [0x0x7ff6fcd97b24+117460]
-	GetHandleVerifier [0x0x7ff6fcd97cdf+117903]
-	GetHandleVerifier [0x0x7ff6fcd7dbb8+11112]
+	GetHandleVerifier [0x0x7ff733e0e8e5+80021]
+	GetHandleVerifier [0x0x7ff733e0e940+80112]
+	(No symbol) [0x0x7ff733b9060f]
+	(No symbol) [0x0x7ff733be8854]
+	(No symbol) [0x0x7ff733be8b1c]
+	(No symbol) [0x0x7ff733c3c927]
+	(No symbol) [0x0x7ff733c1126f]
+	(No symbol) [0x0x7ff733c3968a]
+	(No symbol) [0x0x7ff733c11003]
+	(No symbol) [0x0x7ff733bd95d1]
+	(No symbol) [0x0x7ff733bda3f3]
+	GetHandleVerifier [0x0x7ff7340cdc7d+2960429]
+	GetHandleVerifier [0x0x7ff7340c7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7340e8977+3070247]
+	GetHandleVerifier [0x0x7ff733e283ce+185214]
+	GetHandleVerifier [0x0x7ff733e2fe1f+216527]
+	GetHandleVerifier [0x0x7ff733e17b24+117460]
+	GetHandleVerifier [0x0x7ff733e17cdf+117903]
+	GetHandleVerifier [0x0x7ff733dfdbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -712,25 +712,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6fcd8e8e5+80021]
-	GetHandleVerifier [0x0x7ff6fcd8e940+80112]
-	(No symbol) [0x0x7ff6fcb1060f]
-	(No symbol) [0x0x7ff6fcb68854]
-	(No symbol) [0x0x7ff6fcb68b1c]
-	(No symbol) [0x0x7ff6fcbbc927]
-	(No symbol) [0x0x7ff6fcb9126f]
-	(No symbol) [0x0x7ff6fcbb968a]
-	(No symbol) [0x0x7ff6fcb91003]
-	(No symbol) [0x0x7ff6fcb595d1]
-	(No symbol) [0x0x7ff6fcb5a3f3]
-	GetHandleVerifier [0x0x7ff6fd04dc7d+2960429]
-	GetHandleVerifier [0x0x7ff6fd047f3a+2936554]
-	GetHandleVerifier [0x0x7ff6fd068977+3070247]
-	GetHandleVerifier [0x0x7ff6fcda83ce+185214]
-	GetHandleVerifier [0x0x7ff6fcdafe1f+216527]
-	GetHandleVerifier [0x0x7ff6fcd97b24+117460]
-	GetHandleVerifier [0x0x7ff6fcd97cdf+117903]
-	GetHandleVerifier [0x0x7ff6fcd7dbb8+11112]
+	GetHandleVerifier [0x0x7ff733e0e8e5+80021]
+	GetHandleVerifier [0x0x7ff733e0e940+80112]
+	(No symbol) [0x0x7ff733b9060f]
+	(No symbol) [0x0x7ff733be8854]
+	(No symbol) [0x0x7ff733be8b1c]
+	(No symbol) [0x0x7ff733c3c927]
+	(No symbol) [0x0x7ff733c1126f]
+	(No symbol) [0x0x7ff733c3968a]
+	(No symbol) [0x0x7ff733c11003]
+	(No symbol) [0x0x7ff733bd95d1]
+	(No symbol) [0x0x7ff733bda3f3]
+	GetHandleVerifier [0x0x7ff7340cdc7d+2960429]
+	GetHandleVerifier [0x0x7ff7340c7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7340e8977+3070247]
+	GetHandleVerifier [0x0x7ff733e283ce+185214]
+	GetHandleVerifier [0x0x7ff733e2fe1f+216527]
+	GetHandleVerifier [0x0x7ff733e17b24+117460]
+	GetHandleVerifier [0x0x7ff733e17cdf+117903]
+	GetHandleVerifier [0x0x7ff733dfdbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -833,25 +833,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6fcd8e8e5+80021]
-	GetHandleVerifier [0x0x7ff6fcd8e940+80112]
-	(No symbol) [0x0x7ff6fcb1060f]
-	(No symbol) [0x0x7ff6fcb68854]
-	(No symbol) [0x0x7ff6fcb68b1c]
-	(No symbol) [0x0x7ff6fcbbc927]
-	(No symbol) [0x0x7ff6fcb9126f]
-	(No symbol) [0x0x7ff6fcbb968a]
-	(No symbol) [0x0x7ff6fcb91003]
-	(No symbol) [0x0x7ff6fcb595d1]
-	(No symbol) [0x0x7ff6fcb5a3f3]
-	GetHandleVerifier [0x0x7ff6fd04dc7d+2960429]
-	GetHandleVerifier [0x0x7ff6fd047f3a+2936554]
-	GetHandleVerifier [0x0x7ff6fd068977+3070247]
-	GetHandleVerifier [0x0x7ff6fcda83ce+185214]
-	GetHandleVerifier [0x0x7ff6fcdafe1f+216527]
-	GetHandleVerifier [0x0x7ff6fcd97b24+117460]
-	GetHandleVerifier [0x0x7ff6fcd97cdf+117903]
-	GetHandleVerifier [0x0x7ff6fcd7dbb8+11112]
+	GetHandleVerifier [0x0x7ff733e0e8e5+80021]
+	GetHandleVerifier [0x0x7ff733e0e940+80112]
+	(No symbol) [0x0x7ff733b9060f]
+	(No symbol) [0x0x7ff733be8854]
+	(No symbol) [0x0x7ff733be8b1c]
+	(No symbol) [0x0x7ff733c3c927]
+	(No symbol) [0x0x7ff733c1126f]
+	(No symbol) [0x0x7ff733c3968a]
+	(No symbol) [0x0x7ff733c11003]
+	(No symbol) [0x0x7ff733bd95d1]
+	(No symbol) [0x0x7ff733bda3f3]
+	GetHandleVerifier [0x0x7ff7340cdc7d+2960429]
+	GetHandleVerifier [0x0x7ff7340c7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7340e8977+3070247]
+	GetHandleVerifier [0x0x7ff733e283ce+185214]
+	GetHandleVerifier [0x0x7ff733e2fe1f+216527]
+	GetHandleVerifier [0x0x7ff733e17b24+117460]
+	GetHandleVerifier [0x0x7ff733e17cdf+117903]
+	GetHandleVerifier [0x0x7ff733dfdbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -954,25 +954,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6fcd8e8e5+80021]
-	GetHandleVerifier [0x0x7ff6fcd8e940+80112]
-	(No symbol) [0x0x7ff6fcb1060f]
-	(No symbol) [0x0x7ff6fcb68854]
-	(No symbol) [0x0x7ff6fcb68b1c]
-	(No symbol) [0x0x7ff6fcbbc927]
-	(No symbol) [0x0x7ff6fcb9126f]
-	(No symbol) [0x0x7ff6fcbb968a]
-	(No symbol) [0x0x7ff6fcb91003]
-	(No symbol) [0x0x7ff6fcb595d1]
-	(No symbol) [0x0x7ff6fcb5a3f3]
-	GetHandleVerifier [0x0x7ff6fd04dc7d+2960429]
-	GetHandleVerifier [0x0x7ff6fd047f3a+2936554]
-	GetHandleVerifier [0x0x7ff6fd068977+3070247]
-	GetHandleVerifier [0x0x7ff6fcda83ce+185214]
-	GetHandleVerifier [0x0x7ff6fcdafe1f+216527]
-	GetHandleVerifier [0x0x7ff6fcd97b24+117460]
-	GetHandleVerifier [0x0x7ff6fcd97cdf+117903]
-	GetHandleVerifier [0x0x7ff6fcd7dbb8+11112]
+	GetHandleVerifier [0x0x7ff733e0e8e5+80021]
+	GetHandleVerifier [0x0x7ff733e0e940+80112]
+	(No symbol) [0x0x7ff733b9060f]
+	(No symbol) [0x0x7ff733be8854]
+	(No symbol) [0x0x7ff733be8b1c]
+	(No symbol) [0x0x7ff733c3c927]
+	(No symbol) [0x0x7ff733c1126f]
+	(No symbol) [0x0x7ff733c3968a]
+	(No symbol) [0x0x7ff733c11003]
+	(No symbol) [0x0x7ff733bd95d1]
+	(No symbol) [0x0x7ff733bda3f3]
+	GetHandleVerifier [0x0x7ff7340cdc7d+2960429]
+	GetHandleVerifier [0x0x7ff7340c7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7340e8977+3070247]
+	GetHandleVerifier [0x0x7ff733e283ce+185214]
+	GetHandleVerifier [0x0x7ff733e2fe1f+216527]
+	GetHandleVerifier [0x0x7ff733e17b24+117460]
+	GetHandleVerifier [0x0x7ff733e17cdf+117903]
+	GetHandleVerifier [0x0x7ff733dfdbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -1075,25 +1075,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6fcd8e8e5+80021]
-	GetHandleVerifier [0x0x7ff6fcd8e940+80112]
-	(No symbol) [0x0x7ff6fcb1060f]
-	(No symbol) [0x0x7ff6fcb68854]
-	(No symbol) [0x0x7ff6fcb68b1c]
-	(No symbol) [0x0x7ff6fcbbc927]
-	(No symbol) [0x0x7ff6fcb9126f]
-	(No symbol) [0x0x7ff6fcbb968a]
-	(No symbol) [0x0x7ff6fcb91003]
-	(No symbol) [0x0x7ff6fcb595d1]
-	(No symbol) [0x0x7ff6fcb5a3f3]
-	GetHandleVerifier [0x0x7ff6fd04dc7d+2960429]
-	GetHandleVerifier [0x0x7ff6fd047f3a+2936554]
-	GetHandleVerifier [0x0x7ff6fd068977+3070247]
-	GetHandleVerifier [0x0x7ff6fcda83ce+185214]
-	GetHandleVerifier [0x0x7ff6fcdafe1f+216527]
-	GetHandleVerifier [0x0x7ff6fcd97b24+117460]
-	GetHandleVerifier [0x0x7ff6fcd97cdf+117903]
-	GetHandleVerifier [0x0x7ff6fcd7dbb8+11112]
+	GetHandleVerifier [0x0x7ff733e0e8e5+80021]
+	GetHandleVerifier [0x0x7ff733e0e940+80112]
+	(No symbol) [0x0x7ff733b9060f]
+	(No symbol) [0x0x7ff733be8854]
+	(No symbol) [0x0x7ff733be8b1c]
+	(No symbol) [0x0x7ff733c3c927]
+	(No symbol) [0x0x7ff733c1126f]
+	(No symbol) [0x0x7ff733c3968a]
+	(No symbol) [0x0x7ff733c11003]
+	(No symbol) [0x0x7ff733bd95d1]
+	(No symbol) [0x0x7ff733bda3f3]
+	GetHandleVerifier [0x0x7ff7340cdc7d+2960429]
+	GetHandleVerifier [0x0x7ff7340c7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7340e8977+3070247]
+	GetHandleVerifier [0x0x7ff733e283ce+185214]
+	GetHandleVerifier [0x0x7ff733e2fe1f+216527]
+	GetHandleVerifier [0x0x7ff733e17b24+117460]
+	GetHandleVerifier [0x0x7ff733e17cdf+117903]
+	GetHandleVerifier [0x0x7ff733dfdbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -1196,25 +1196,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6fcd8e8e5+80021]
-	GetHandleVerifier [0x0x7ff6fcd8e940+80112]
-	(No symbol) [0x0x7ff6fcb1060f]
-	(No symbol) [0x0x7ff6fcb68854]
-	(No symbol) [0x0x7ff6fcb68b1c]
-	(No symbol) [0x0x7ff6fcbbc927]
-	(No symbol) [0x0x7ff6fcb9126f]
-	(No symbol) [0x0x7ff6fcbb968a]
-	(No symbol) [0x0x7ff6fcb91003]
-	(No symbol) [0x0x7ff6fcb595d1]
-	(No symbol) [0x0x7ff6fcb5a3f3]
-	GetHandleVerifier [0x0x7ff6fd04dc7d+2960429]
-	GetHandleVerifier [0x0x7ff6fd047f3a+2936554]
-	GetHandleVerifier [0x0x7ff6fd068977+3070247]
-	GetHandleVerifier [0x0x7ff6fcda83ce+185214]
-	GetHandleVerifier [0x0x7ff6fcdafe1f+216527]
-	GetHandleVerifier [0x0x7ff6fcd97b24+117460]
-	GetHandleVerifier [0x0x7ff6fcd97cdf+117903]
-	GetHandleVerifier [0x0x7ff6fcd7dbb8+11112]
+	GetHandleVerifier [0x0x7ff733e0e8e5+80021]
+	GetHandleVerifier [0x0x7ff733e0e940+80112]
+	(No symbol) [0x0x7ff733b9060f]
+	(No symbol) [0x0x7ff733be8854]
+	(No symbol) [0x0x7ff733be8b1c]
+	(No symbol) [0x0x7ff733c3c927]
+	(No symbol) [0x0x7ff733c1126f]
+	(No symbol) [0x0x7ff733c3968a]
+	(No symbol) [0x0x7ff733c11003]
+	(No symbol) [0x0x7ff733bd95d1]
+	(No symbol) [0x0x7ff733bda3f3]
+	GetHandleVerifier [0x0x7ff7340cdc7d+2960429]
+	GetHandleVerifier [0x0x7ff7340c7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7340e8977+3070247]
+	GetHandleVerifier [0x0x7ff733e283ce+185214]
+	GetHandleVerifier [0x0x7ff733e2fe1f+216527]
+	GetHandleVerifier [0x0x7ff733e17b24+117460]
+	GetHandleVerifier [0x0x7ff733e17cdf+117903]
+	GetHandleVerifier [0x0x7ff733dfdbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -1317,25 +1317,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6fcd8e8e5+80021]
-	GetHandleVerifier [0x0x7ff6fcd8e940+80112]
-	(No symbol) [0x0x7ff6fcb1060f]
-	(No symbol) [0x0x7ff6fcb68854]
-	(No symbol) [0x0x7ff6fcb68b1c]
-	(No symbol) [0x0x7ff6fcbbc927]
-	(No symbol) [0x0x7ff6fcb9126f]
-	(No symbol) [0x0x7ff6fcbb968a]
-	(No symbol) [0x0x7ff6fcb91003]
-	(No symbol) [0x0x7ff6fcb595d1]
-	(No symbol) [0x0x7ff6fcb5a3f3]
-	GetHandleVerifier [0x0x7ff6fd04dc7d+2960429]
-	GetHandleVerifier [0x0x7ff6fd047f3a+2936554]
-	GetHandleVerifier [0x0x7ff6fd068977+3070247]
-	GetHandleVerifier [0x0x7ff6fcda83ce+185214]
-	GetHandleVerifier [0x0x7ff6fcdafe1f+216527]
-	GetHandleVerifier [0x0x7ff6fcd97b24+117460]
-	GetHandleVerifier [0x0x7ff6fcd97cdf+117903]
-	GetHandleVerifier [0x0x7ff6fcd7dbb8+11112]
+	GetHandleVerifier [0x0x7ff733e0e8e5+80021]
+	GetHandleVerifier [0x0x7ff733e0e940+80112]
+	(No symbol) [0x0x7ff733b9060f]
+	(No symbol) [0x0x7ff733be8854]
+	(No symbol) [0x0x7ff733be8b1c]
+	(No symbol) [0x0x7ff733c3c927]
+	(No symbol) [0x0x7ff733c1126f]
+	(No symbol) [0x0x7ff733c3968a]
+	(No symbol) [0x0x7ff733c11003]
+	(No symbol) [0x0x7ff733bd95d1]
+	(No symbol) [0x0x7ff733bda3f3]
+	GetHandleVerifier [0x0x7ff7340cdc7d+2960429]
+	GetHandleVerifier [0x0x7ff7340c7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7340e8977+3070247]
+	GetHandleVerifier [0x0x7ff733e283ce+185214]
+	GetHandleVerifier [0x0x7ff733e2fe1f+216527]
+	GetHandleVerifier [0x0x7ff733e17b24+117460]
+	GetHandleVerifier [0x0x7ff733e17cdf+117903]
+	GetHandleVerifier [0x0x7ff733dfdbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -1438,25 +1438,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6fcd8e8e5+80021]
-	GetHandleVerifier [0x0x7ff6fcd8e940+80112]
-	(No symbol) [0x0x7ff6fcb1060f]
-	(No symbol) [0x0x7ff6fcb68854]
-	(No symbol) [0x0x7ff6fcb68b1c]
-	(No symbol) [0x0x7ff6fcbbc927]
-	(No symbol) [0x0x7ff6fcb9126f]
-	(No symbol) [0x0x7ff6fcbb968a]
-	(No symbol) [0x0x7ff6fcb91003]
-	(No symbol) [0x0x7ff6fcb595d1]
-	(No symbol) [0x0x7ff6fcb5a3f3]
-	GetHandleVerifier [0x0x7ff6fd04dc7d+2960429]
-	GetHandleVerifier [0x0x7ff6fd047f3a+2936554]
-	GetHandleVerifier [0x0x7ff6fd068977+3070247]
-	GetHandleVerifier [0x0x7ff6fcda83ce+185214]
-	GetHandleVerifier [0x0x7ff6fcdafe1f+216527]
-	GetHandleVerifier [0x0x7ff6fcd97b24+117460]
-	GetHandleVerifier [0x0x7ff6fcd97cdf+117903]
-	GetHandleVerifier [0x0x7ff6fcd7dbb8+11112]
+	GetHandleVerifier [0x0x7ff733e0e8e5+80021]
+	GetHandleVerifier [0x0x7ff733e0e940+80112]
+	(No symbol) [0x0x7ff733b9060f]
+	(No symbol) [0x0x7ff733be8854]
+	(No symbol) [0x0x7ff733be8b1c]
+	(No symbol) [0x0x7ff733c3c927]
+	(No symbol) [0x0x7ff733c1126f]
+	(No symbol) [0x0x7ff733c3968a]
+	(No symbol) [0x0x7ff733c11003]
+	(No symbol) [0x0x7ff733bd95d1]
+	(No symbol) [0x0x7ff733bda3f3]
+	GetHandleVerifier [0x0x7ff7340cdc7d+2960429]
+	GetHandleVerifier [0x0x7ff7340c7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7340e8977+3070247]
+	GetHandleVerifier [0x0x7ff733e283ce+185214]
+	GetHandleVerifier [0x0x7ff733e2fe1f+216527]
+	GetHandleVerifier [0x0x7ff733e17b24+117460]
+	GetHandleVerifier [0x0x7ff733e17cdf+117903]
+	GetHandleVerifier [0x0x7ff733dfdbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -1559,25 +1559,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6fcd8e8e5+80021]
-	GetHandleVerifier [0x0x7ff6fcd8e940+80112]
-	(No symbol) [0x0x7ff6fcb1060f]
-	(No symbol) [0x0x7ff6fcb68854]
-	(No symbol) [0x0x7ff6fcb68b1c]
-	(No symbol) [0x0x7ff6fcbbc927]
-	(No symbol) [0x0x7ff6fcb9126f]
-	(No symbol) [0x0x7ff6fcbb968a]
-	(No symbol) [0x0x7ff6fcb91003]
-	(No symbol) [0x0x7ff6fcb595d1]
-	(No symbol) [0x0x7ff6fcb5a3f3]
-	GetHandleVerifier [0x0x7ff6fd04dc7d+2960429]
-	GetHandleVerifier [0x0x7ff6fd047f3a+2936554]
-	GetHandleVerifier [0x0x7ff6fd068977+3070247]
-	GetHandleVerifier [0x0x7ff6fcda83ce+185214]
-	GetHandleVerifier [0x0x7ff6fcdafe1f+216527]
-	GetHandleVerifier [0x0x7ff6fcd97b24+117460]
-	GetHandleVerifier [0x0x7ff6fcd97cdf+117903]
-	GetHandleVerifier [0x0x7ff6fcd7dbb8+11112]
+	GetHandleVerifier [0x0x7ff733e0e8e5+80021]
+	GetHandleVerifier [0x0x7ff733e0e940+80112]
+	(No symbol) [0x0x7ff733b9060f]
+	(No symbol) [0x0x7ff733be8854]
+	(No symbol) [0x0x7ff733be8b1c]
+	(No symbol) [0x0x7ff733c3c927]
+	(No symbol) [0x0x7ff733c1126f]
+	(No symbol) [0x0x7ff733c3968a]
+	(No symbol) [0x0x7ff733c11003]
+	(No symbol) [0x0x7ff733bd95d1]
+	(No symbol) [0x0x7ff733bda3f3]
+	GetHandleVerifier [0x0x7ff7340cdc7d+2960429]
+	GetHandleVerifier [0x0x7ff7340c7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7340e8977+3070247]
+	GetHandleVerifier [0x0x7ff733e283ce+185214]
+	GetHandleVerifier [0x0x7ff733e2fe1f+216527]
+	GetHandleVerifier [0x0x7ff733e17b24+117460]
+	GetHandleVerifier [0x0x7ff733e17cdf+117903]
+	GetHandleVerifier [0x0x7ff733dfdbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -1680,25 +1680,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6fcd8e8e5+80021]
-	GetHandleVerifier [0x0x7ff6fcd8e940+80112]
-	(No symbol) [0x0x7ff6fcb1060f]
-	(No symbol) [0x0x7ff6fcb68854]
-	(No symbol) [0x0x7ff6fcb68b1c]
-	(No symbol) [0x0x7ff6fcbbc927]
-	(No symbol) [0x0x7ff6fcb9126f]
-	(No symbol) [0x0x7ff6fcbb968a]
-	(No symbol) [0x0x7ff6fcb91003]
-	(No symbol) [0x0x7ff6fcb595d1]
-	(No symbol) [0x0x7ff6fcb5a3f3]
-	GetHandleVerifier [0x0x7ff6fd04dc7d+2960429]
-	GetHandleVerifier [0x0x7ff6fd047f3a+2936554]
-	GetHandleVerifier [0x0x7ff6fd068977+3070247]
-	GetHandleVerifier [0x0x7ff6fcda83ce+185214]
-	GetHandleVerifier [0x0x7ff6fcdafe1f+216527]
-	GetHandleVerifier [0x0x7ff6fcd97b24+117460]
-	GetHandleVerifier [0x0x7ff6fcd97cdf+117903]
-	GetHandleVerifier [0x0x7ff6fcd7dbb8+11112]
+	GetHandleVerifier [0x0x7ff733e0e8e5+80021]
+	GetHandleVerifier [0x0x7ff733e0e940+80112]
+	(No symbol) [0x0x7ff733b9060f]
+	(No symbol) [0x0x7ff733be8854]
+	(No symbol) [0x0x7ff733be8b1c]
+	(No symbol) [0x0x7ff733c3c927]
+	(No symbol) [0x0x7ff733c1126f]
+	(No symbol) [0x0x7ff733c3968a]
+	(No symbol) [0x0x7ff733c11003]
+	(No symbol) [0x0x7ff733bd95d1]
+	(No symbol) [0x0x7ff733bda3f3]
+	GetHandleVerifier [0x0x7ff7340cdc7d+2960429]
+	GetHandleVerifier [0x0x7ff7340c7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7340e8977+3070247]
+	GetHandleVerifier [0x0x7ff733e283ce+185214]
+	GetHandleVerifier [0x0x7ff733e2fe1f+216527]
+	GetHandleVerifier [0x0x7ff733e17b24+117460]
+	GetHandleVerifier [0x0x7ff733e17cdf+117903]
+	GetHandleVerifier [0x0x7ff733dfdbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -1801,25 +1801,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6fcd8e8e5+80021]
-	GetHandleVerifier [0x0x7ff6fcd8e940+80112]
-	(No symbol) [0x0x7ff6fcb1060f]
-	(No symbol) [0x0x7ff6fcb68854]
-	(No symbol) [0x0x7ff6fcb68b1c]
-	(No symbol) [0x0x7ff6fcbbc927]
-	(No symbol) [0x0x7ff6fcb9126f]
-	(No symbol) [0x0x7ff6fcbb968a]
-	(No symbol) [0x0x7ff6fcb91003]
-	(No symbol) [0x0x7ff6fcb595d1]
-	(No symbol) [0x0x7ff6fcb5a3f3]
-	GetHandleVerifier [0x0x7ff6fd04dc7d+2960429]
-	GetHandleVerifier [0x0x7ff6fd047f3a+2936554]
-	GetHandleVerifier [0x0x7ff6fd068977+3070247]
-	GetHandleVerifier [0x0x7ff6fcda83ce+185214]
-	GetHandleVerifier [0x0x7ff6fcdafe1f+216527]
-	GetHandleVerifier [0x0x7ff6fcd97b24+117460]
-	GetHandleVerifier [0x0x7ff6fcd97cdf+117903]
-	GetHandleVerifier [0x0x7ff6fcd7dbb8+11112]
+	GetHandleVerifier [0x0x7ff733e0e8e5+80021]
+	GetHandleVerifier [0x0x7ff733e0e940+80112]
+	(No symbol) [0x0x7ff733b9060f]
+	(No symbol) [0x0x7ff733be8854]
+	(No symbol) [0x0x7ff733be8b1c]
+	(No symbol) [0x0x7ff733c3c927]
+	(No symbol) [0x0x7ff733c1126f]
+	(No symbol) [0x0x7ff733c3968a]
+	(No symbol) [0x0x7ff733c11003]
+	(No symbol) [0x0x7ff733bd95d1]
+	(No symbol) [0x0x7ff733bda3f3]
+	GetHandleVerifier [0x0x7ff7340cdc7d+2960429]
+	GetHandleVerifier [0x0x7ff7340c7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7340e8977+3070247]
+	GetHandleVerifier [0x0x7ff733e283ce+185214]
+	GetHandleVerifier [0x0x7ff733e2fe1f+216527]
+	GetHandleVerifier [0x0x7ff733e17b24+117460]
+	GetHandleVerifier [0x0x7ff733e17cdf+117903]
+	GetHandleVerifier [0x0x7ff733dfdbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -1922,25 +1922,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6fcd8e8e5+80021]
-	GetHandleVerifier [0x0x7ff6fcd8e940+80112]
-	(No symbol) [0x0x7ff6fcb1060f]
-	(No symbol) [0x0x7ff6fcb68854]
-	(No symbol) [0x0x7ff6fcb68b1c]
-	(No symbol) [0x0x7ff6fcbbc927]
-	(No symbol) [0x0x7ff6fcb9126f]
-	(No symbol) [0x0x7ff6fcbb968a]
-	(No symbol) [0x0x7ff6fcb91003]
-	(No symbol) [0x0x7ff6fcb595d1]
-	(No symbol) [0x0x7ff6fcb5a3f3]
-	GetHandleVerifier [0x0x7ff6fd04dc7d+2960429]
-	GetHandleVerifier [0x0x7ff6fd047f3a+2936554]
-	GetHandleVerifier [0x0x7ff6fd068977+3070247]
-	GetHandleVerifier [0x0x7ff6fcda83ce+185214]
-	GetHandleVerifier [0x0x7ff6fcdafe1f+216527]
-	GetHandleVerifier [0x0x7ff6fcd97b24+117460]
-	GetHandleVerifier [0x0x7ff6fcd97cdf+117903]
-	GetHandleVerifier [0x0x7ff6fcd7dbb8+11112]
+	GetHandleVerifier [0x0x7ff733e0e8e5+80021]
+	GetHandleVerifier [0x0x7ff733e0e940+80112]
+	(No symbol) [0x0x7ff733b9060f]
+	(No symbol) [0x0x7ff733be8854]
+	(No symbol) [0x0x7ff733be8b1c]
+	(No symbol) [0x0x7ff733c3c927]
+	(No symbol) [0x0x7ff733c1126f]
+	(No symbol) [0x0x7ff733c3968a]
+	(No symbol) [0x0x7ff733c11003]
+	(No symbol) [0x0x7ff733bd95d1]
+	(No symbol) [0x0x7ff733bda3f3]
+	GetHandleVerifier [0x0x7ff7340cdc7d+2960429]
+	GetHandleVerifier [0x0x7ff7340c7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7340e8977+3070247]
+	GetHandleVerifier [0x0x7ff733e283ce+185214]
+	GetHandleVerifier [0x0x7ff733e2fe1f+216527]
+	GetHandleVerifier [0x0x7ff733e17b24+117460]
+	GetHandleVerifier [0x0x7ff733e17cdf+117903]
+	GetHandleVerifier [0x0x7ff733dfdbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>£39.81</t>
+          <t>£38.53</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2043,25 +2043,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6fcd8e8e5+80021]
-	GetHandleVerifier [0x0x7ff6fcd8e940+80112]
-	(No symbol) [0x0x7ff6fcb1060f]
-	(No symbol) [0x0x7ff6fcb68854]
-	(No symbol) [0x0x7ff6fcb68b1c]
-	(No symbol) [0x0x7ff6fcbbc927]
-	(No symbol) [0x0x7ff6fcb9126f]
-	(No symbol) [0x0x7ff6fcbb968a]
-	(No symbol) [0x0x7ff6fcb91003]
-	(No symbol) [0x0x7ff6fcb595d1]
-	(No symbol) [0x0x7ff6fcb5a3f3]
-	GetHandleVerifier [0x0x7ff6fd04dc7d+2960429]
-	GetHandleVerifier [0x0x7ff6fd047f3a+2936554]
-	GetHandleVerifier [0x0x7ff6fd068977+3070247]
-	GetHandleVerifier [0x0x7ff6fcda83ce+185214]
-	GetHandleVerifier [0x0x7ff6fcdafe1f+216527]
-	GetHandleVerifier [0x0x7ff6fcd97b24+117460]
-	GetHandleVerifier [0x0x7ff6fcd97cdf+117903]
-	GetHandleVerifier [0x0x7ff6fcd7dbb8+11112]
+	GetHandleVerifier [0x0x7ff733e0e8e5+80021]
+	GetHandleVerifier [0x0x7ff733e0e940+80112]
+	(No symbol) [0x0x7ff733b9060f]
+	(No symbol) [0x0x7ff733be8854]
+	(No symbol) [0x0x7ff733be8b1c]
+	(No symbol) [0x0x7ff733c3c927]
+	(No symbol) [0x0x7ff733c1126f]
+	(No symbol) [0x0x7ff733c3968a]
+	(No symbol) [0x0x7ff733c11003]
+	(No symbol) [0x0x7ff733bd95d1]
+	(No symbol) [0x0x7ff733bda3f3]
+	GetHandleVerifier [0x0x7ff7340cdc7d+2960429]
+	GetHandleVerifier [0x0x7ff7340c7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7340e8977+3070247]
+	GetHandleVerifier [0x0x7ff733e283ce+185214]
+	GetHandleVerifier [0x0x7ff733e2fe1f+216527]
+	GetHandleVerifier [0x0x7ff733e17b24+117460]
+	GetHandleVerifier [0x0x7ff733e17cdf+117903]
+	GetHandleVerifier [0x0x7ff733dfdbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>£38.66</t>
+          <t>£38.64</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2164,25 +2164,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6fcd8e8e5+80021]
-	GetHandleVerifier [0x0x7ff6fcd8e940+80112]
-	(No symbol) [0x0x7ff6fcb1060f]
-	(No symbol) [0x0x7ff6fcb68854]
-	(No symbol) [0x0x7ff6fcb68b1c]
-	(No symbol) [0x0x7ff6fcbbc927]
-	(No symbol) [0x0x7ff6fcb9126f]
-	(No symbol) [0x0x7ff6fcbb968a]
-	(No symbol) [0x0x7ff6fcb91003]
-	(No symbol) [0x0x7ff6fcb595d1]
-	(No symbol) [0x0x7ff6fcb5a3f3]
-	GetHandleVerifier [0x0x7ff6fd04dc7d+2960429]
-	GetHandleVerifier [0x0x7ff6fd047f3a+2936554]
-	GetHandleVerifier [0x0x7ff6fd068977+3070247]
-	GetHandleVerifier [0x0x7ff6fcda83ce+185214]
-	GetHandleVerifier [0x0x7ff6fcdafe1f+216527]
-	GetHandleVerifier [0x0x7ff6fcd97b24+117460]
-	GetHandleVerifier [0x0x7ff6fcd97cdf+117903]
-	GetHandleVerifier [0x0x7ff6fcd7dbb8+11112]
+	GetHandleVerifier [0x0x7ff733e0e8e5+80021]
+	GetHandleVerifier [0x0x7ff733e0e940+80112]
+	(No symbol) [0x0x7ff733b9060f]
+	(No symbol) [0x0x7ff733be8854]
+	(No symbol) [0x0x7ff733be8b1c]
+	(No symbol) [0x0x7ff733c3c927]
+	(No symbol) [0x0x7ff733c1126f]
+	(No symbol) [0x0x7ff733c3968a]
+	(No symbol) [0x0x7ff733c11003]
+	(No symbol) [0x0x7ff733bd95d1]
+	(No symbol) [0x0x7ff733bda3f3]
+	GetHandleVerifier [0x0x7ff7340cdc7d+2960429]
+	GetHandleVerifier [0x0x7ff7340c7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7340e8977+3070247]
+	GetHandleVerifier [0x0x7ff733e283ce+185214]
+	GetHandleVerifier [0x0x7ff733e2fe1f+216527]
+	GetHandleVerifier [0x0x7ff733e17b24+117460]
+	GetHandleVerifier [0x0x7ff733e17cdf+117903]
+	GetHandleVerifier [0x0x7ff733dfdbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -2285,25 +2285,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6fcd8e8e5+80021]
-	GetHandleVerifier [0x0x7ff6fcd8e940+80112]
-	(No symbol) [0x0x7ff6fcb1060f]
-	(No symbol) [0x0x7ff6fcb68854]
-	(No symbol) [0x0x7ff6fcb68b1c]
-	(No symbol) [0x0x7ff6fcbbc927]
-	(No symbol) [0x0x7ff6fcb9126f]
-	(No symbol) [0x0x7ff6fcbb968a]
-	(No symbol) [0x0x7ff6fcb91003]
-	(No symbol) [0x0x7ff6fcb595d1]
-	(No symbol) [0x0x7ff6fcb5a3f3]
-	GetHandleVerifier [0x0x7ff6fd04dc7d+2960429]
-	GetHandleVerifier [0x0x7ff6fd047f3a+2936554]
-	GetHandleVerifier [0x0x7ff6fd068977+3070247]
-	GetHandleVerifier [0x0x7ff6fcda83ce+185214]
-	GetHandleVerifier [0x0x7ff6fcdafe1f+216527]
-	GetHandleVerifier [0x0x7ff6fcd97b24+117460]
-	GetHandleVerifier [0x0x7ff6fcd97cdf+117903]
-	GetHandleVerifier [0x0x7ff6fcd7dbb8+11112]
+	GetHandleVerifier [0x0x7ff733e0e8e5+80021]
+	GetHandleVerifier [0x0x7ff733e0e940+80112]
+	(No symbol) [0x0x7ff733b9060f]
+	(No symbol) [0x0x7ff733be8854]
+	(No symbol) [0x0x7ff733be8b1c]
+	(No symbol) [0x0x7ff733c3c927]
+	(No symbol) [0x0x7ff733c1126f]
+	(No symbol) [0x0x7ff733c3968a]
+	(No symbol) [0x0x7ff733c11003]
+	(No symbol) [0x0x7ff733bd95d1]
+	(No symbol) [0x0x7ff733bda3f3]
+	GetHandleVerifier [0x0x7ff7340cdc7d+2960429]
+	GetHandleVerifier [0x0x7ff7340c7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7340e8977+3070247]
+	GetHandleVerifier [0x0x7ff733e283ce+185214]
+	GetHandleVerifier [0x0x7ff733e2fe1f+216527]
+	GetHandleVerifier [0x0x7ff733e17b24+117460]
+	GetHandleVerifier [0x0x7ff733e17cdf+117903]
+	GetHandleVerifier [0x0x7ff733dfdbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -2503,25 +2503,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6fcd8e8e5+80021]
-	GetHandleVerifier [0x0x7ff6fcd8e940+80112]
-	(No symbol) [0x0x7ff6fcb1060f]
-	(No symbol) [0x0x7ff6fcb68854]
-	(No symbol) [0x0x7ff6fcb68b1c]
-	(No symbol) [0x0x7ff6fcbbc927]
-	(No symbol) [0x0x7ff6fcb9126f]
-	(No symbol) [0x0x7ff6fcbb968a]
-	(No symbol) [0x0x7ff6fcb91003]
-	(No symbol) [0x0x7ff6fcb595d1]
-	(No symbol) [0x0x7ff6fcb5a3f3]
-	GetHandleVerifier [0x0x7ff6fd04dc7d+2960429]
-	GetHandleVerifier [0x0x7ff6fd047f3a+2936554]
-	GetHandleVerifier [0x0x7ff6fd068977+3070247]
-	GetHandleVerifier [0x0x7ff6fcda83ce+185214]
-	GetHandleVerifier [0x0x7ff6fcdafe1f+216527]
-	GetHandleVerifier [0x0x7ff6fcd97b24+117460]
-	GetHandleVerifier [0x0x7ff6fcd97cdf+117903]
-	GetHandleVerifier [0x0x7ff6fcd7dbb8+11112]
+	GetHandleVerifier [0x0x7ff733e0e8e5+80021]
+	GetHandleVerifier [0x0x7ff733e0e940+80112]
+	(No symbol) [0x0x7ff733b9060f]
+	(No symbol) [0x0x7ff733be8854]
+	(No symbol) [0x0x7ff733be8b1c]
+	(No symbol) [0x0x7ff733c3c927]
+	(No symbol) [0x0x7ff733c1126f]
+	(No symbol) [0x0x7ff733c3968a]
+	(No symbol) [0x0x7ff733c11003]
+	(No symbol) [0x0x7ff733bd95d1]
+	(No symbol) [0x0x7ff733bda3f3]
+	GetHandleVerifier [0x0x7ff7340cdc7d+2960429]
+	GetHandleVerifier [0x0x7ff7340c7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7340e8977+3070247]
+	GetHandleVerifier [0x0x7ff733e283ce+185214]
+	GetHandleVerifier [0x0x7ff733e2fe1f+216527]
+	GetHandleVerifier [0x0x7ff733e17b24+117460]
+	GetHandleVerifier [0x0x7ff733e17cdf+117903]
+	GetHandleVerifier [0x0x7ff733dfdbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -2601,7 +2601,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>£28.99</t>
+          <t>Error: 'NoneType' object has no attribute 'find'</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2624,25 +2624,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6fcd8e8e5+80021]
-	GetHandleVerifier [0x0x7ff6fcd8e940+80112]
-	(No symbol) [0x0x7ff6fcb1060f]
-	(No symbol) [0x0x7ff6fcb68854]
-	(No symbol) [0x0x7ff6fcb68b1c]
-	(No symbol) [0x0x7ff6fcbbc927]
-	(No symbol) [0x0x7ff6fcb9126f]
-	(No symbol) [0x0x7ff6fcbb968a]
-	(No symbol) [0x0x7ff6fcb91003]
-	(No symbol) [0x0x7ff6fcb595d1]
-	(No symbol) [0x0x7ff6fcb5a3f3]
-	GetHandleVerifier [0x0x7ff6fd04dc7d+2960429]
-	GetHandleVerifier [0x0x7ff6fd047f3a+2936554]
-	GetHandleVerifier [0x0x7ff6fd068977+3070247]
-	GetHandleVerifier [0x0x7ff6fcda83ce+185214]
-	GetHandleVerifier [0x0x7ff6fcdafe1f+216527]
-	GetHandleVerifier [0x0x7ff6fcd97b24+117460]
-	GetHandleVerifier [0x0x7ff6fcd97cdf+117903]
-	GetHandleVerifier [0x0x7ff6fcd7dbb8+11112]
+	GetHandleVerifier [0x0x7ff733e0e8e5+80021]
+	GetHandleVerifier [0x0x7ff733e0e940+80112]
+	(No symbol) [0x0x7ff733b9060f]
+	(No symbol) [0x0x7ff733be8854]
+	(No symbol) [0x0x7ff733be8b1c]
+	(No symbol) [0x0x7ff733c3c927]
+	(No symbol) [0x0x7ff733c1126f]
+	(No symbol) [0x0x7ff733c3968a]
+	(No symbol) [0x0x7ff733c11003]
+	(No symbol) [0x0x7ff733bd95d1]
+	(No symbol) [0x0x7ff733bda3f3]
+	GetHandleVerifier [0x0x7ff7340cdc7d+2960429]
+	GetHandleVerifier [0x0x7ff7340c7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7340e8977+3070247]
+	GetHandleVerifier [0x0x7ff733e283ce+185214]
+	GetHandleVerifier [0x0x7ff733e2fe1f+216527]
+	GetHandleVerifier [0x0x7ff733e17b24+117460]
+	GetHandleVerifier [0x0x7ff733e17cdf+117903]
+	GetHandleVerifier [0x0x7ff733dfdbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -2745,25 +2745,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6fcd8e8e5+80021]
-	GetHandleVerifier [0x0x7ff6fcd8e940+80112]
-	(No symbol) [0x0x7ff6fcb1060f]
-	(No symbol) [0x0x7ff6fcb68854]
-	(No symbol) [0x0x7ff6fcb68b1c]
-	(No symbol) [0x0x7ff6fcbbc927]
-	(No symbol) [0x0x7ff6fcb9126f]
-	(No symbol) [0x0x7ff6fcbb968a]
-	(No symbol) [0x0x7ff6fcb91003]
-	(No symbol) [0x0x7ff6fcb595d1]
-	(No symbol) [0x0x7ff6fcb5a3f3]
-	GetHandleVerifier [0x0x7ff6fd04dc7d+2960429]
-	GetHandleVerifier [0x0x7ff6fd047f3a+2936554]
-	GetHandleVerifier [0x0x7ff6fd068977+3070247]
-	GetHandleVerifier [0x0x7ff6fcda83ce+185214]
-	GetHandleVerifier [0x0x7ff6fcdafe1f+216527]
-	GetHandleVerifier [0x0x7ff6fcd97b24+117460]
-	GetHandleVerifier [0x0x7ff6fcd97cdf+117903]
-	GetHandleVerifier [0x0x7ff6fcd7dbb8+11112]
+	GetHandleVerifier [0x0x7ff733e0e8e5+80021]
+	GetHandleVerifier [0x0x7ff733e0e940+80112]
+	(No symbol) [0x0x7ff733b9060f]
+	(No symbol) [0x0x7ff733be8854]
+	(No symbol) [0x0x7ff733be8b1c]
+	(No symbol) [0x0x7ff733c3c927]
+	(No symbol) [0x0x7ff733c1126f]
+	(No symbol) [0x0x7ff733c3968a]
+	(No symbol) [0x0x7ff733c11003]
+	(No symbol) [0x0x7ff733bd95d1]
+	(No symbol) [0x0x7ff733bda3f3]
+	GetHandleVerifier [0x0x7ff7340cdc7d+2960429]
+	GetHandleVerifier [0x0x7ff7340c7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7340e8977+3070247]
+	GetHandleVerifier [0x0x7ff733e283ce+185214]
+	GetHandleVerifier [0x0x7ff733e2fe1f+216527]
+	GetHandleVerifier [0x0x7ff733e17b24+117460]
+	GetHandleVerifier [0x0x7ff733e17cdf+117903]
+	GetHandleVerifier [0x0x7ff733dfdbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -2866,25 +2866,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6fcd8e8e5+80021]
-	GetHandleVerifier [0x0x7ff6fcd8e940+80112]
-	(No symbol) [0x0x7ff6fcb1060f]
-	(No symbol) [0x0x7ff6fcb68854]
-	(No symbol) [0x0x7ff6fcb68b1c]
-	(No symbol) [0x0x7ff6fcbbc927]
-	(No symbol) [0x0x7ff6fcb9126f]
-	(No symbol) [0x0x7ff6fcbb968a]
-	(No symbol) [0x0x7ff6fcb91003]
-	(No symbol) [0x0x7ff6fcb595d1]
-	(No symbol) [0x0x7ff6fcb5a3f3]
-	GetHandleVerifier [0x0x7ff6fd04dc7d+2960429]
-	GetHandleVerifier [0x0x7ff6fd047f3a+2936554]
-	GetHandleVerifier [0x0x7ff6fd068977+3070247]
-	GetHandleVerifier [0x0x7ff6fcda83ce+185214]
-	GetHandleVerifier [0x0x7ff6fcdafe1f+216527]
-	GetHandleVerifier [0x0x7ff6fcd97b24+117460]
-	GetHandleVerifier [0x0x7ff6fcd97cdf+117903]
-	GetHandleVerifier [0x0x7ff6fcd7dbb8+11112]
+	GetHandleVerifier [0x0x7ff733e0e8e5+80021]
+	GetHandleVerifier [0x0x7ff733e0e940+80112]
+	(No symbol) [0x0x7ff733b9060f]
+	(No symbol) [0x0x7ff733be8854]
+	(No symbol) [0x0x7ff733be8b1c]
+	(No symbol) [0x0x7ff733c3c927]
+	(No symbol) [0x0x7ff733c1126f]
+	(No symbol) [0x0x7ff733c3968a]
+	(No symbol) [0x0x7ff733c11003]
+	(No symbol) [0x0x7ff733bd95d1]
+	(No symbol) [0x0x7ff733bda3f3]
+	GetHandleVerifier [0x0x7ff7340cdc7d+2960429]
+	GetHandleVerifier [0x0x7ff7340c7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7340e8977+3070247]
+	GetHandleVerifier [0x0x7ff733e283ce+185214]
+	GetHandleVerifier [0x0x7ff733e2fe1f+216527]
+	GetHandleVerifier [0x0x7ff733e17b24+117460]
+	GetHandleVerifier [0x0x7ff733e17cdf+117903]
+	GetHandleVerifier [0x0x7ff733dfdbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -2987,25 +2987,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6fcd8e8e5+80021]
-	GetHandleVerifier [0x0x7ff6fcd8e940+80112]
-	(No symbol) [0x0x7ff6fcb1060f]
-	(No symbol) [0x0x7ff6fcb68854]
-	(No symbol) [0x0x7ff6fcb68b1c]
-	(No symbol) [0x0x7ff6fcbbc927]
-	(No symbol) [0x0x7ff6fcb9126f]
-	(No symbol) [0x0x7ff6fcbb968a]
-	(No symbol) [0x0x7ff6fcb91003]
-	(No symbol) [0x0x7ff6fcb595d1]
-	(No symbol) [0x0x7ff6fcb5a3f3]
-	GetHandleVerifier [0x0x7ff6fd04dc7d+2960429]
-	GetHandleVerifier [0x0x7ff6fd047f3a+2936554]
-	GetHandleVerifier [0x0x7ff6fd068977+3070247]
-	GetHandleVerifier [0x0x7ff6fcda83ce+185214]
-	GetHandleVerifier [0x0x7ff6fcdafe1f+216527]
-	GetHandleVerifier [0x0x7ff6fcd97b24+117460]
-	GetHandleVerifier [0x0x7ff6fcd97cdf+117903]
-	GetHandleVerifier [0x0x7ff6fcd7dbb8+11112]
+	GetHandleVerifier [0x0x7ff733e0e8e5+80021]
+	GetHandleVerifier [0x0x7ff733e0e940+80112]
+	(No symbol) [0x0x7ff733b9060f]
+	(No symbol) [0x0x7ff733be8854]
+	(No symbol) [0x0x7ff733be8b1c]
+	(No symbol) [0x0x7ff733c3c927]
+	(No symbol) [0x0x7ff733c1126f]
+	(No symbol) [0x0x7ff733c3968a]
+	(No symbol) [0x0x7ff733c11003]
+	(No symbol) [0x0x7ff733bd95d1]
+	(No symbol) [0x0x7ff733bda3f3]
+	GetHandleVerifier [0x0x7ff7340cdc7d+2960429]
+	GetHandleVerifier [0x0x7ff7340c7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7340e8977+3070247]
+	GetHandleVerifier [0x0x7ff733e283ce+185214]
+	GetHandleVerifier [0x0x7ff733e2fe1f+216527]
+	GetHandleVerifier [0x0x7ff733e17b24+117460]
+	GetHandleVerifier [0x0x7ff733e17cdf+117903]
+	GetHandleVerifier [0x0x7ff733dfdbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -3108,25 +3108,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6fcd8e8e5+80021]
-	GetHandleVerifier [0x0x7ff6fcd8e940+80112]
-	(No symbol) [0x0x7ff6fcb1060f]
-	(No symbol) [0x0x7ff6fcb68854]
-	(No symbol) [0x0x7ff6fcb68b1c]
-	(No symbol) [0x0x7ff6fcbbc927]
-	(No symbol) [0x0x7ff6fcb9126f]
-	(No symbol) [0x0x7ff6fcbb968a]
-	(No symbol) [0x0x7ff6fcb91003]
-	(No symbol) [0x0x7ff6fcb595d1]
-	(No symbol) [0x0x7ff6fcb5a3f3]
-	GetHandleVerifier [0x0x7ff6fd04dc7d+2960429]
-	GetHandleVerifier [0x0x7ff6fd047f3a+2936554]
-	GetHandleVerifier [0x0x7ff6fd068977+3070247]
-	GetHandleVerifier [0x0x7ff6fcda83ce+185214]
-	GetHandleVerifier [0x0x7ff6fcdafe1f+216527]
-	GetHandleVerifier [0x0x7ff6fcd97b24+117460]
-	GetHandleVerifier [0x0x7ff6fcd97cdf+117903]
-	GetHandleVerifier [0x0x7ff6fcd7dbb8+11112]
+	GetHandleVerifier [0x0x7ff733e0e8e5+80021]
+	GetHandleVerifier [0x0x7ff733e0e940+80112]
+	(No symbol) [0x0x7ff733b9060f]
+	(No symbol) [0x0x7ff733be8854]
+	(No symbol) [0x0x7ff733be8b1c]
+	(No symbol) [0x0x7ff733c3c927]
+	(No symbol) [0x0x7ff733c1126f]
+	(No symbol) [0x0x7ff733c3968a]
+	(No symbol) [0x0x7ff733c11003]
+	(No symbol) [0x0x7ff733bd95d1]
+	(No symbol) [0x0x7ff733bda3f3]
+	GetHandleVerifier [0x0x7ff7340cdc7d+2960429]
+	GetHandleVerifier [0x0x7ff7340c7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7340e8977+3070247]
+	GetHandleVerifier [0x0x7ff733e283ce+185214]
+	GetHandleVerifier [0x0x7ff733e2fe1f+216527]
+	GetHandleVerifier [0x0x7ff733e17b24+117460]
+	GetHandleVerifier [0x0x7ff733e17cdf+117903]
+	GetHandleVerifier [0x0x7ff733dfdbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -3229,25 +3229,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6fcd8e8e5+80021]
-	GetHandleVerifier [0x0x7ff6fcd8e940+80112]
-	(No symbol) [0x0x7ff6fcb1060f]
-	(No symbol) [0x0x7ff6fcb68854]
-	(No symbol) [0x0x7ff6fcb68b1c]
-	(No symbol) [0x0x7ff6fcbbc927]
-	(No symbol) [0x0x7ff6fcb9126f]
-	(No symbol) [0x0x7ff6fcbb968a]
-	(No symbol) [0x0x7ff6fcb91003]
-	(No symbol) [0x0x7ff6fcb595d1]
-	(No symbol) [0x0x7ff6fcb5a3f3]
-	GetHandleVerifier [0x0x7ff6fd04dc7d+2960429]
-	GetHandleVerifier [0x0x7ff6fd047f3a+2936554]
-	GetHandleVerifier [0x0x7ff6fd068977+3070247]
-	GetHandleVerifier [0x0x7ff6fcda83ce+185214]
-	GetHandleVerifier [0x0x7ff6fcdafe1f+216527]
-	GetHandleVerifier [0x0x7ff6fcd97b24+117460]
-	GetHandleVerifier [0x0x7ff6fcd97cdf+117903]
-	GetHandleVerifier [0x0x7ff6fcd7dbb8+11112]
+	GetHandleVerifier [0x0x7ff733e0e8e5+80021]
+	GetHandleVerifier [0x0x7ff733e0e940+80112]
+	(No symbol) [0x0x7ff733b9060f]
+	(No symbol) [0x0x7ff733be8854]
+	(No symbol) [0x0x7ff733be8b1c]
+	(No symbol) [0x0x7ff733c3c927]
+	(No symbol) [0x0x7ff733c1126f]
+	(No symbol) [0x0x7ff733c3968a]
+	(No symbol) [0x0x7ff733c11003]
+	(No symbol) [0x0x7ff733bd95d1]
+	(No symbol) [0x0x7ff733bda3f3]
+	GetHandleVerifier [0x0x7ff7340cdc7d+2960429]
+	GetHandleVerifier [0x0x7ff7340c7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7340e8977+3070247]
+	GetHandleVerifier [0x0x7ff733e283ce+185214]
+	GetHandleVerifier [0x0x7ff733e2fe1f+216527]
+	GetHandleVerifier [0x0x7ff733e17b24+117460]
+	GetHandleVerifier [0x0x7ff733e17cdf+117903]
+	GetHandleVerifier [0x0x7ff733dfdbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -3350,25 +3350,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6fcd8e8e5+80021]
-	GetHandleVerifier [0x0x7ff6fcd8e940+80112]
-	(No symbol) [0x0x7ff6fcb1060f]
-	(No symbol) [0x0x7ff6fcb68854]
-	(No symbol) [0x0x7ff6fcb68b1c]
-	(No symbol) [0x0x7ff6fcbbc927]
-	(No symbol) [0x0x7ff6fcb9126f]
-	(No symbol) [0x0x7ff6fcbb968a]
-	(No symbol) [0x0x7ff6fcb91003]
-	(No symbol) [0x0x7ff6fcb595d1]
-	(No symbol) [0x0x7ff6fcb5a3f3]
-	GetHandleVerifier [0x0x7ff6fd04dc7d+2960429]
-	GetHandleVerifier [0x0x7ff6fd047f3a+2936554]
-	GetHandleVerifier [0x0x7ff6fd068977+3070247]
-	GetHandleVerifier [0x0x7ff6fcda83ce+185214]
-	GetHandleVerifier [0x0x7ff6fcdafe1f+216527]
-	GetHandleVerifier [0x0x7ff6fcd97b24+117460]
-	GetHandleVerifier [0x0x7ff6fcd97cdf+117903]
-	GetHandleVerifier [0x0x7ff6fcd7dbb8+11112]
+	GetHandleVerifier [0x0x7ff733e0e8e5+80021]
+	GetHandleVerifier [0x0x7ff733e0e940+80112]
+	(No symbol) [0x0x7ff733b9060f]
+	(No symbol) [0x0x7ff733be8854]
+	(No symbol) [0x0x7ff733be8b1c]
+	(No symbol) [0x0x7ff733c3c927]
+	(No symbol) [0x0x7ff733c1126f]
+	(No symbol) [0x0x7ff733c3968a]
+	(No symbol) [0x0x7ff733c11003]
+	(No symbol) [0x0x7ff733bd95d1]
+	(No symbol) [0x0x7ff733bda3f3]
+	GetHandleVerifier [0x0x7ff7340cdc7d+2960429]
+	GetHandleVerifier [0x0x7ff7340c7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7340e8977+3070247]
+	GetHandleVerifier [0x0x7ff733e283ce+185214]
+	GetHandleVerifier [0x0x7ff733e2fe1f+216527]
+	GetHandleVerifier [0x0x7ff733e17b24+117460]
+	GetHandleVerifier [0x0x7ff733e17cdf+117903]
+	GetHandleVerifier [0x0x7ff733dfdbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -3471,25 +3471,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6fcd8e8e5+80021]
-	GetHandleVerifier [0x0x7ff6fcd8e940+80112]
-	(No symbol) [0x0x7ff6fcb1060f]
-	(No symbol) [0x0x7ff6fcb68854]
-	(No symbol) [0x0x7ff6fcb68b1c]
-	(No symbol) [0x0x7ff6fcbbc927]
-	(No symbol) [0x0x7ff6fcb9126f]
-	(No symbol) [0x0x7ff6fcbb968a]
-	(No symbol) [0x0x7ff6fcb91003]
-	(No symbol) [0x0x7ff6fcb595d1]
-	(No symbol) [0x0x7ff6fcb5a3f3]
-	GetHandleVerifier [0x0x7ff6fd04dc7d+2960429]
-	GetHandleVerifier [0x0x7ff6fd047f3a+2936554]
-	GetHandleVerifier [0x0x7ff6fd068977+3070247]
-	GetHandleVerifier [0x0x7ff6fcda83ce+185214]
-	GetHandleVerifier [0x0x7ff6fcdafe1f+216527]
-	GetHandleVerifier [0x0x7ff6fcd97b24+117460]
-	GetHandleVerifier [0x0x7ff6fcd97cdf+117903]
-	GetHandleVerifier [0x0x7ff6fcd7dbb8+11112]
+	GetHandleVerifier [0x0x7ff733e0e8e5+80021]
+	GetHandleVerifier [0x0x7ff733e0e940+80112]
+	(No symbol) [0x0x7ff733b9060f]
+	(No symbol) [0x0x7ff733be8854]
+	(No symbol) [0x0x7ff733be8b1c]
+	(No symbol) [0x0x7ff733c3c927]
+	(No symbol) [0x0x7ff733c1126f]
+	(No symbol) [0x0x7ff733c3968a]
+	(No symbol) [0x0x7ff733c11003]
+	(No symbol) [0x0x7ff733bd95d1]
+	(No symbol) [0x0x7ff733bda3f3]
+	GetHandleVerifier [0x0x7ff7340cdc7d+2960429]
+	GetHandleVerifier [0x0x7ff7340c7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7340e8977+3070247]
+	GetHandleVerifier [0x0x7ff733e283ce+185214]
+	GetHandleVerifier [0x0x7ff733e2fe1f+216527]
+	GetHandleVerifier [0x0x7ff733e17b24+117460]
+	GetHandleVerifier [0x0x7ff733e17cdf+117903]
+	GetHandleVerifier [0x0x7ff733dfdbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
